--- a/output/pdf_financials_xlsx/CCB.xlsx
+++ b/output/pdf_financials_xlsx/CCB.xlsx
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.565378</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>12.467048</v>
+        <v>0.104854</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.098553</v>
+        <v>0.003477</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="17">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.257689</v>
+        <v>-1.257689</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6.181097</v>
+        <v>-6.181097</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.047538</v>
+        <v>-1.047538</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="21">
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.257689</v>
+        <v>-1.257689</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.181097</v>
+        <v>-6.181097</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.047538</v>
+        <v>-1.047538</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1758,16 +1758,16 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="24">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.565378</v>
+        <v>0.05</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.467048</v>
+        <v>0.104854</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.098553</v>
+        <v>0.003477</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="28">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.565378</v>
+        <v>0.05</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.467048</v>
+        <v>0.104854</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.098553</v>
+        <v>0.003477</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2166,16 +2166,16 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="30">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>50.97451525662105</v>
+        <v>2615.378</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>50.42052457005058</v>
+        <v>5994.955843363152</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>50.08284279691768</v>
+        <v>30227.63876905378</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5307,46 +5307,46 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.391631</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.003704</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.957684</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.829017</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.416952</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.676485</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.616914</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.04467</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.066391</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.970237</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.879652</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.888614</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.888614</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.246081</v>
       </c>
     </row>
     <row r="93">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-2.384816</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>4.008937</v>
@@ -9142,7 +9142,11 @@
           <t>Reserves (Note 13) 1,370,974</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10626,7 +10630,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -11104,7 +11112,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -15052,7 +15064,11 @@
           <t>Reserves 3,714,565</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>2.391631</v>
       </c>
@@ -22128,7 +22144,11 @@
           <t>Write-off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -22472,7 +22492,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -24236,16 +24260,16 @@
         </is>
       </c>
       <c r="O196" s="5" t="n">
-        <v>0.688704</v>
+        <v>-0.688704</v>
       </c>
       <c r="P196" s="5" t="n">
-        <v>1.002511</v>
+        <v>-1.002511</v>
       </c>
       <c r="Q196" s="5" t="n">
-        <v>2.087997</v>
+        <v>-2.087997</v>
       </c>
       <c r="R196" s="5" t="n">
-        <v>1.263149</v>
+        <v>-1.263149</v>
       </c>
     </row>
     <row r="197">
@@ -25133,10 +25157,10 @@
         </is>
       </c>
       <c r="J207" s="5" t="n">
-        <v>0.565563</v>
+        <v>-0.565563</v>
       </c>
       <c r="K207" s="5" t="n">
-        <v>0.763038</v>
+        <v>-0.763038</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -26477,13 +26501,13 @@
         </is>
       </c>
       <c r="F223" s="5" t="n">
-        <v>1.257689</v>
+        <v>-1.257689</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>6.181097</v>
+        <v>-6.181097</v>
       </c>
       <c r="H223" s="5" t="n">
-        <v>1.047538</v>
+        <v>-1.047538</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CCB.xlsx
+++ b/output/pdf_financials_xlsx/CCB.xlsx
@@ -2435,7 +2435,7 @@
         <v>0.315551</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.864584</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.816604</v>
@@ -2533,7 +2533,7 @@
         <v>0.315551</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.864584</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.816604</v>
@@ -3121,7 +3121,7 @@
         <v>0.019399</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.874984</v>
+        <v>0.0104</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.012525</v>
@@ -8366,7 +8366,11 @@
           <t>Drilling and reclamation deposits (Note 10) 5,000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -9984,7 +9988,11 @@
           <t>Drilling and reclamation deposits (Note 10)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -10942,7 +10950,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11486,7 +11494,11 @@
           <t>Drilling and reclamation deposits (Note 11)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -12206,7 +12218,11 @@
           <t>Drilling and reclamation deposits (Note 12)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -12812,7 +12828,11 @@
           <t>Drilling and reclamation deposits (Note 13)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14284,7 +14304,11 @@
           <t>Drilling and reclamation deposits (Note 13) 20,546</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.127861</v>
       </c>
